--- a/templates/Strukturvorlage_DataDictionary_empty_v1.0.0.xlsx
+++ b/templates/Strukturvorlage_DataDictionary_empty_v1.0.0.xlsx
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C105" s="195" t="inlineStr">
         <is>
-          <t>Der Objekttyp definiert die spezifischen Informationen zu einem Typ, die allen Instanzen dieses Typs gemeinsam sind.</t>
+          <t>Optionale IFC-TypeObject-Entität zur Dokumentation des Mapping-Umfangs. Leer = Mapping gilt nur für die Objektebene. Ausgefüllt = Mapping gilt zusätzlich für die angegebene Typebene; der Wert muss ein schema-konformes Paar mit „IfcObject Entity“ bilden (z. B. IfcTank → IfcTankType). Der PredefinedType wird separat erfasst und validiert.</t>
         </is>
       </c>
       <c r="F105" s="185" t="n"/>
@@ -10780,7 +10780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AI70"/>
+  <dimension ref="A1:AI24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15"/>
   <cols>
     <col width="3.7109375" customWidth="1" style="111" min="1" max="1"/>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="Z2" s="61" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="AA2" s="61" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="Z6" s="106" t="inlineStr">
         <is>
-          <t>validated against IFC 4.3 entity identifiers</t>
+          <t>Leer = nur Objektebene; ausgefüllt = Mapping gilt auch für die angegebene Typebene; validiert gegen IFC 4.3 Objekt-/TypeObject-Paare</t>
         </is>
       </c>
       <c r="AA6" s="106" t="inlineStr">
@@ -12381,52 +12381,6 @@
     <row r="24" ht="12.75" customFormat="1" customHeight="1" s="54">
       <c r="AG24" s="229" t="n"/>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
   </sheetData>
   <dataValidations xWindow="1091" yWindow="456" count="6">
     <dataValidation sqref="AB8:AB1996" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="date" operator="greaterThanOrEqual">
@@ -12467,7 +12421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AK69"/>
+  <dimension ref="A1:AK57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="28.9" customHeight="1"/>
   <cols>
     <col width="3.7109375" customWidth="1" style="100" min="1" max="1"/>
@@ -16034,7 +15988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V68"/>
+  <dimension ref="A1:V55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15"/>
   <cols>
     <col width="3.7109375" customWidth="1" style="44" min="1" max="1"/>
@@ -17626,8 +17580,6 @@
       <c r="U55" s="230" t="n"/>
       <c r="V55" s="230" t="n"/>
     </row>
-    <row r="56"/>
-    <row r="57"/>
     <row r="58" ht="15" customHeight="1" s="223"/>
     <row r="59" ht="15" customHeight="1" s="223"/>
     <row r="60" ht="15" customHeight="1" s="223"/>
@@ -18611,7 +18563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="28.9" customHeight="1"/>
   <cols>
     <col width="3.7109375" customWidth="1" style="100" min="1" max="1"/>

--- a/templates/Strukturvorlage_DataDictionary_empty_v1.0.0.xlsx
+++ b/templates/Strukturvorlage_DataDictionary_empty_v1.0.0.xlsx
@@ -9412,7 +9412,7 @@
       </c>
       <c r="C140" s="195" t="inlineStr">
         <is>
-          <t>Beschreibt eine Liste von Merkmalen / Mebgeb für eine IFC-Entität. Merkmalssätze / Mengensätze, deren Struktur und Eigenschaften fest in der IFC-Spezifikation definiert sind.</t>
+          <t>Referenz auf einen IFC-Merkmals- oder Mengensatz. Ein Einzelwert wird direkt als Pset_*/Qto_*-Name oder zulässige absolute IRI erfasst. Mehrere Werte müssen als gültige JSON-Liste aus nicht leeren Strings mit doppelten Anführungszeichen erfasst werden, z. B. ["Pset_WallCommon", "Qto_WallBaseQuantities"]. Zeilenumbruch-, Semikolon- und einfache Kommalisten sind nicht zulässig.</t>
         </is>
       </c>
       <c r="F140" s="185" t="n"/>
@@ -13242,7 +13242,7 @@
       </c>
       <c r="X6" s="106" t="inlineStr">
         <is>
-          <t>validated against IFC 4.3 property/quantity set identifiers when IFC_URI is present</t>
+          <t>Ein Wert: Pset_* / Qto_* oder zulässige absolute IRI. Mehrere Werte: strikte JSON-Liste, z. B. ["Pset_WallCommon", "Qto_WallBaseQuantities"]; keine Zeilenumbruch-/Semikolonlisten.</t>
         </is>
       </c>
       <c r="Y6" s="106" t="inlineStr">
